--- a/excel/MinigameData.xlsx
+++ b/excel/MinigameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74399C49-83DC-F64F-A9A9-065F6BCDFD3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54BF5330-97C2-134D-A900-53E0BB73271F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5280" yWindow="1800" windowWidth="24120" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
   <si>
     <t>int</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -265,6 +265,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -284,6 +285,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -303,6 +305,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -322,6 +325,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -341,6 +345,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -360,6 +365,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -379,6 +385,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>\n</t>
@@ -398,6 +405,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -417,6 +425,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -436,6 +445,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -455,6 +465,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -474,6 +485,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -493,6 +505,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -512,6 +525,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">! </t>
@@ -531,6 +545,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>?\n</t>
@@ -550,6 +565,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -569,6 +585,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -588,6 +605,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -607,6 +625,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -626,6 +645,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -645,6 +665,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -664,6 +685,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -683,6 +705,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -702,6 +725,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">! </t>
@@ -729,6 +753,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -749,6 +774,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -769,6 +795,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -789,6 +816,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">? </t>
@@ -809,6 +837,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -829,6 +858,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -849,6 +879,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -869,6 +900,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>\n</t>
@@ -889,6 +921,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -909,6 +942,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve">! </t>
@@ -929,6 +963,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -949,6 +984,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -969,6 +1005,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -989,6 +1026,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -1009,6 +1047,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -1029,6 +1068,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>!\n</t>
@@ -1049,6 +1089,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -1069,6 +1110,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -1089,6 +1131,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -1109,6 +1152,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -1129,6 +1173,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -1149,6 +1194,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>!</t>
@@ -1167,6 +1213,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -1187,6 +1234,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -1207,6 +1255,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -1227,6 +1276,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -1247,6 +1297,7 @@
         <sz val="10"/>
         <color rgb="FF000000"/>
         <rFont val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>!</t>
@@ -1320,6 +1371,10 @@
       </rPr>
       <t xml:space="preserve"> (MinigameData)</t>
     </r>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>FamiliarDurationHours</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1453,7 +1508,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1467,7 +1522,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
@@ -1685,17 +1739,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86B6D362-0137-C449-A908-E1D2EE2BB6D0}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="16.33203125" customWidth="1"/>
-    <col min="3" max="3" width="16.5" customWidth="1"/>
-    <col min="4" max="4" width="19" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" customWidth="1"/>
+    <col min="2" max="3" width="16.33203125" customWidth="1"/>
+    <col min="4" max="4" width="16.5" customWidth="1"/>
+    <col min="5" max="5" width="19" customWidth="1"/>
+    <col min="7" max="7" width="14.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="3" t="s">
         <v>13</v>
       </c>
@@ -1706,16 +1760,19 @@
         <v>0</v>
       </c>
       <c r="D1" s="8" t="s">
+        <v>0</v>
+      </c>
+      <c r="E1" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="F1" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F1" s="11" t="s">
+      <c r="G1" s="8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:7">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -1723,19 +1780,22 @@
         <v>14</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
         <v>20</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="F2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="11" t="s">
+      <c r="G2" s="8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15">
+    <row r="3" spans="1:7" ht="15">
       <c r="A3" s="6" t="s">
         <v>3</v>
       </c>
@@ -1743,19 +1803,22 @@
         <v>2</v>
       </c>
       <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3">
         <v>60</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="F3" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="F3" s="12" t="s">
+      <c r="G3" s="11" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15">
+    <row r="4" spans="1:7" ht="15">
       <c r="A4" s="9" t="s">
         <v>1</v>
       </c>
@@ -1763,19 +1826,22 @@
         <v>2</v>
       </c>
       <c r="C4">
+        <v>3</v>
+      </c>
+      <c r="D4">
         <v>60</v>
       </c>
-      <c r="D4" s="8" t="s">
+      <c r="E4" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="F4" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="G4" s="10" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15">
+    <row r="5" spans="1:7" ht="15">
       <c r="A5" s="8" t="s">
         <v>16</v>
       </c>
@@ -1783,15 +1849,18 @@
         <v>2</v>
       </c>
       <c r="C5">
+        <v>3</v>
+      </c>
+      <c r="D5">
         <v>60</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="E5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="13" t="s">
+      <c r="F5" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="G5" s="8" t="s">
         <v>32</v>
       </c>
     </row>

--- a/excel/MinigameData.xlsx
+++ b/excel/MinigameData.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/geugkkom/Documents/Tsomsomm/lunaria-data/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54BF5330-97C2-134D-A900-53E0BB73271F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{34EF97CE-47E2-F54C-8ADE-966376DFBF91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5280" yWindow="1800" windowWidth="24120" windowHeight="15400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="37">
   <si>
     <t>int</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -1375,6 +1375,59 @@
   </si>
   <si>
     <t>FamiliarDurationHours</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>[</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>하급</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>_</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>접착제</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>]</t>
+    </r>
+  </si>
+  <si>
+    <t>FamiliarRewardIds</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>FamiliarRewardQuantities</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1739,17 +1792,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86B6D362-0137-C449-A908-E1D2EE2BB6D0}">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:I5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="22" customWidth="1"/>
     <col min="2" max="3" width="16.33203125" customWidth="1"/>
     <col min="4" max="4" width="16.5" customWidth="1"/>
     <col min="5" max="5" width="19" customWidth="1"/>
-    <col min="7" max="7" width="14.6640625" customWidth="1"/>
+    <col min="7" max="7" width="20.6640625" customWidth="1"/>
+    <col min="8" max="8" width="18.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:9">
       <c r="A1" s="3" t="s">
         <v>13</v>
       </c>
@@ -1771,8 +1825,14 @@
       <c r="G1" s="8" t="s">
         <v>25</v>
       </c>
+      <c r="H1" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>15</v>
+      </c>
     </row>
-    <row r="2" spans="1:7">
+    <row r="2" spans="1:9">
       <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
@@ -1794,8 +1854,14 @@
       <c r="G2" s="8" t="s">
         <v>27</v>
       </c>
+      <c r="H2" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>36</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" ht="15">
+    <row r="3" spans="1:9" ht="15">
       <c r="A3" s="6" t="s">
         <v>3</v>
       </c>
@@ -1817,8 +1883,14 @@
       <c r="G3" s="11" t="s">
         <v>28</v>
       </c>
+      <c r="H3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" ht="15">
+    <row r="4" spans="1:9" ht="15">
       <c r="A4" s="9" t="s">
         <v>1</v>
       </c>
@@ -1840,8 +1912,14 @@
       <c r="G4" s="10" t="s">
         <v>24</v>
       </c>
+      <c r="H4" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="8">
+        <v>20</v>
+      </c>
     </row>
-    <row r="5" spans="1:7" ht="15">
+    <row r="5" spans="1:9" ht="15">
       <c r="A5" s="8" t="s">
         <v>16</v>
       </c>
@@ -1862,6 +1940,12 @@
       </c>
       <c r="G5" s="8" t="s">
         <v>32</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="I5" s="8">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
